--- a/assets/templates/Template_Format_Data.xlsx
+++ b/assets/templates/Template_Format_Data.xlsx
@@ -1,40 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d4c18ed4402bc1f/Pictures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aplikasi\xampp\htdocs\spk_mahasiswa\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F46B432C-2629-480C-A6FD-2F87B2462E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8444EFB4-47A4-46A2-AD6C-36719E12C14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>NIM</t>
   </si>
@@ -76,13 +62,16 @@
   </si>
   <si>
     <t xml:space="preserve">Absensi </t>
+  </si>
+  <si>
+    <t>Status SIA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +90,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -110,7 +107,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -187,11 +184,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -211,7 +219,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -494,29 +506,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" customWidth="1"/>
-    <col min="2" max="2" width="36.54296875" customWidth="1"/>
-    <col min="3" max="3" width="44.81640625" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" customWidth="1"/>
-    <col min="7" max="7" width="16.81640625" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" customWidth="1"/>
-    <col min="9" max="9" width="16.453125" customWidth="1"/>
-    <col min="10" max="10" width="15.54296875" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" customWidth="1"/>
-    <col min="12" max="12" width="11.7265625" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" customWidth="1"/>
+    <col min="3" max="3" width="44.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
@@ -549,11 +561,14 @@
       <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O1" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C2" s="6"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -567,7 +582,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C3" s="6"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -581,7 +596,7 @@
       <c r="M3" s="1"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C4" s="6"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -595,7 +610,7 @@
       <c r="M4" s="1"/>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C5" s="6"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -609,7 +624,7 @@
       <c r="M5" s="1"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C6" s="6"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -623,7 +638,7 @@
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C7" s="6"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -637,7 +652,7 @@
       <c r="M7" s="1"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C8" s="6"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -651,7 +666,7 @@
       <c r="M8" s="1"/>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C9" s="6"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -665,7 +680,7 @@
       <c r="M9" s="1"/>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C10" s="6"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -679,7 +694,7 @@
       <c r="M10" s="1"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C11" s="6"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -693,7 +708,7 @@
       <c r="M11" s="1"/>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C12" s="6"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -707,7 +722,7 @@
       <c r="M12" s="1"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C13" s="6"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -721,7 +736,7 @@
       <c r="M13" s="1"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C14" s="6"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -735,7 +750,7 @@
       <c r="M14" s="1"/>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C15" s="6"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -749,7 +764,7 @@
       <c r="M15" s="1"/>
       <c r="N15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C16" s="6"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -763,7 +778,7 @@
       <c r="M16" s="1"/>
       <c r="N16" s="2"/>
     </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C17" s="6"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -777,7 +792,7 @@
       <c r="M17" s="1"/>
       <c r="N17" s="2"/>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C18" s="6"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -791,7 +806,7 @@
       <c r="M18" s="1"/>
       <c r="N18" s="2"/>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C19" s="6"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -805,7 +820,7 @@
       <c r="M19" s="1"/>
       <c r="N19" s="2"/>
     </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C20" s="6"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -819,7 +834,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="2"/>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C21" s="6"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -833,7 +848,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="2"/>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C22" s="6"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -847,7 +862,7 @@
       <c r="M22" s="1"/>
       <c r="N22" s="2"/>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C23" s="6"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -861,7 +876,7 @@
       <c r="M23" s="1"/>
       <c r="N23" s="2"/>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C24" s="6"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -875,7 +890,7 @@
       <c r="M24" s="1"/>
       <c r="N24" s="2"/>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C25" s="6"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -889,7 +904,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C26" s="6"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -903,7 +918,7 @@
       <c r="M26" s="1"/>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C27" s="6"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -917,7 +932,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C28" s="6"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -933,5 +948,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>